--- a/enterprise documentation/PCB Design/PickAndPlace_BridgePCB3.xlsx
+++ b/enterprise documentation/PCB Design/PickAndPlace_BridgePCB3.xlsx
@@ -4,14 +4,14 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet sheetId="1" name="PickAndPlace_BridgePCB3" state="visible" r:id="rId4"/>
+    <sheet sheetId="1" name="PickAndPlace_PCB-3_2026-08-15" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1190" uniqueCount="320">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1202" uniqueCount="326">
   <si>
     <t>Designator</t>
   </si>
@@ -971,6 +971,24 @@
   </si>
   <si>
     <t>67.31mm</t>
+  </si>
+  <si>
+    <t>R213</t>
+  </si>
+  <si>
+    <t>0603WAF0000T5E</t>
+  </si>
+  <si>
+    <t>33.02mm</t>
+  </si>
+  <si>
+    <t>91.694mm</t>
+  </si>
+  <si>
+    <t>92.447mm</t>
+  </si>
+  <si>
+    <t>0Ω</t>
   </si>
 </sst>
 </file>
@@ -1347,7 +1365,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N99"/>
+  <dimension ref="A1:N100"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="14" width="20" customWidth="1"/>
@@ -5709,6 +5727,50 @@
         <v>36</v>
       </c>
     </row>
+    <row r="100" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>320</v>
+      </c>
+      <c r="B100" t="s">
+        <v>321</v>
+      </c>
+      <c r="C100" t="s">
+        <v>31</v>
+      </c>
+      <c r="D100" t="s">
+        <v>322</v>
+      </c>
+      <c r="E100" t="s">
+        <v>323</v>
+      </c>
+      <c r="F100" t="s">
+        <v>322</v>
+      </c>
+      <c r="G100" t="s">
+        <v>323</v>
+      </c>
+      <c r="H100" t="s">
+        <v>322</v>
+      </c>
+      <c r="I100" t="s">
+        <v>324</v>
+      </c>
+      <c r="J100">
+        <v>2</v>
+      </c>
+      <c r="K100" t="s">
+        <v>21</v>
+      </c>
+      <c r="L100">
+        <v>270</v>
+      </c>
+      <c r="M100" t="s">
+        <v>22</v>
+      </c>
+      <c r="N100" t="s">
+        <v>325</v>
+      </c>
+    </row>
   </sheetData>
   <printOptions gridLines="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
